--- a/mex_urls.xlsx
+++ b/mex_urls.xlsx
@@ -1133,12 +1133,12 @@
     <t>https://fbref.com/en/matches/7b6538c4/Queretaro-Pachuca-August-20-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/79c2aa6a/Necaxa-UANL-August-20-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4e9d84a2/America-Atlas-August-20-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/79c2aa6a/Necaxa-UANL-August-20-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3d881e40/Mazatlan-Puebla-August-22-2023-Liga-MX</t>
   </si>
   <si>
@@ -1265,12 +1265,12 @@
     <t>https://fbref.com/en/matches/d2197878/Cruz-Azul-Queretaro-September-24-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e28dfbe1/Leon-Tijuana-September-23-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b550b761/Guadalajara-Pachuca-September-23-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e28dfbe1/Leon-Tijuana-September-23-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d3c7c413/UANL-Monterrey-September-23-2023-Liga-MX</t>
   </si>
   <si>
@@ -1310,18 +1310,18 @@
     <t>https://fbref.com/en/matches/2165d0d0/America-Pachuca-October-3-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/35a78eee/Necaxa-Cruz-Azul-October-4-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/031cb346/Pumas-UNAM-Queretaro-October-4-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/35a78eee/Necaxa-Cruz-Azul-October-4-2023-Liga-MX</t>
+    <t>https://fbref.com/en/matches/3d4ca1d4/UANL-Toluca-October-4-2023-Liga-MX</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1f0d0da7/Santos-Laguna-Tijuana-October-4-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d4ca1d4/UANL-Toluca-October-4-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/35209303/Monterrey-FC-Juarez-October-7-2023-Liga-MX</t>
   </si>
   <si>
@@ -1418,12 +1418,12 @@
     <t>https://fbref.com/en/matches/378e5ac6/Queretaro-Guadalajara-October-31-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7407560a/Leon-Pumas-UNAM-October-31-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5ce71d69/Monterrey-Necaxa-October-31-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7407560a/Leon-Pumas-UNAM-October-31-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0e41aef6/Cruz-Azul-FC-Juarez-November-1-2023-Liga-MX</t>
   </si>
   <si>
@@ -1469,12 +1469,12 @@
     <t>https://fbref.com/en/matches/e15c1a07/Monterrey-Santos-Laguna-November-8-2023-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fa4c796c/Atletico-Santos-Laguna-November-11-2023-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/540232e3/Queretaro-Monterrey-November-11-2023-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fa4c796c/Atletico-Santos-Laguna-November-11-2023-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c56981e5/Mazatlan-Toluca-November-10-2023-Liga-MX</t>
   </si>
   <si>
@@ -1556,12 +1556,12 @@
     <t>https://fbref.com/en/matches/4db8c47c/Pumas-UNAM-FC-Juarez-January-14-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5f787ed2/Tijuana-America-January-13-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/012864cd/Cruz-Azul-Pachuca-January-13-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5f787ed2/Tijuana-America-January-13-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6f5ab25f/Guadalajara-Santos-Laguna-January-13-2024-Liga-MX</t>
   </si>
   <si>
@@ -1598,21 +1598,21 @@
     <t>https://fbref.com/en/matches/a33e5fbc/Santos-Laguna-Monterrey-January-21-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8d0be42a/Atletico-UANL-January-24-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/58a0b02c/Monterrey-Queretaro-January-24-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8d0be42a/Atletico-UANL-January-24-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fdbb9d04/FC-Juarez-America-January-24-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9787800b/Leon-Santos-Laguna-January-27-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0d3de91a/Cruz-Azul-Mazatlan-January-27-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9787800b/Leon-Santos-Laguna-January-27-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6229fd6d/Tijuana-Guadalajara-January-26-2024-Liga-MX</t>
   </si>
   <si>
@@ -1703,12 +1703,12 @@
     <t>https://fbref.com/en/matches/ef8a5ea5/Cruz-Azul-Atletico-February-10-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/818ef662/Santos-Laguna-UANL-February-10-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2681bdd7/Monterrey-Pachuca-February-10-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/818ef662/Santos-Laguna-UANL-February-10-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2681f9a4/Atlas-Pumas-UNAM-February-14-2024-Liga-MX</t>
   </si>
   <si>
@@ -1781,21 +1781,21 @@
     <t>https://fbref.com/en/matches/9fc26aa2/Queretaro-Atletico-February-27-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e9f9b822/UANL-FC-Juarez-February-28-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/df4574ac/Tijuana-Monterrey-February-28-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e9f9b822/UANL-FC-Juarez-February-28-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/dac5413c/Toluca-UANL-March-2-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d17bb5e2/Queretaro-Santos-Laguna-March-1-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0ba3c159/Atletico-Puebla-March-1-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d17bb5e2/Queretaro-Santos-Laguna-March-1-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4973734a/Mazatlan-Necaxa-March-1-2024-Liga-MX</t>
   </si>
   <si>
@@ -1808,12 +1808,12 @@
     <t>https://fbref.com/en/matches/24bded1f/Atlas-America-March-2-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/db8b6c40/Tijuana-Leon-March-3-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3d9b464b/Monterrey-Pumas-UNAM-March-3-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/db8b6c40/Tijuana-Leon-March-3-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9a04edec/Guadalajara-Leon-March-9-2024-Liga-MX</t>
   </si>
   <si>
@@ -1862,12 +1862,12 @@
     <t>https://fbref.com/en/matches/3952b7e3/Guadalajara-America-March-16-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e5e1618e/Toluca-Pumas-UNAM-March-17-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c58f665b/Atletico-Pachuca-March-17-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e5e1618e/Toluca-Pumas-UNAM-March-17-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/54e1f8da/FC-Juarez-Puebla-March-23-2024-Liga-MX</t>
   </si>
   <si>
@@ -1883,12 +1883,12 @@
     <t>https://fbref.com/en/matches/87cb0b67/Atlas-Queretaro-March-31-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cf6f17d9/Pachuca-Toluca-March-30-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7e8a1562/Monterrey-Guadalajara-March-30-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cf6f17d9/Pachuca-Toluca-March-30-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d4fde25d/Pumas-UNAM-Cruz-Azul-March-30-2024-Liga-MX</t>
   </si>
   <si>
@@ -1943,12 +1943,12 @@
     <t>https://fbref.com/en/matches/d2097b1b/Monterrey-UANL-April-13-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f7d68a7c/Pumas-UNAM-Leon-April-14-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a6eae94e/Atlas-Atletico-April-14-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f7d68a7c/Pumas-UNAM-Leon-April-14-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e7f6b1f5/FC-Juarez-Tijuana-April-14-2024-Liga-MX</t>
   </si>
   <si>
@@ -1967,12 +1967,12 @@
     <t>https://fbref.com/en/matches/590dce39/UANL-Necaxa-April-20-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b8055aa6/Santos-Laguna-Pachuca-April-20-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/746e5777/Guadalajara-Queretaro-April-20-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b8055aa6/Santos-Laguna-Pachuca-April-20-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2c78241f/Pumas-UNAM-America-April-20-2024-Liga-MX</t>
   </si>
   <si>
@@ -1988,22 +1988,22 @@
     <t>https://fbref.com/en/matches/e33b5e15/Queretaro-Pumas-UNAM-April-26-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ca622d65/UANL-Tijuana-April-27-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c5197c83/Toluca-Cruz-Azul-April-27-2024-Liga-MX</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ca622d65/UANL-Tijuana-April-27-2024-Liga-MX</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1727c3c4/Pachuca-Mazatlan-April-27-2024-Liga-MX</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/2fb3c3e0/Atlas-Guadalajara-April-27-2024-Liga-MX</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/55754ab7/Santos-Laguna-Atletico-April-28-2024-Liga-MX</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4136ce8b/Necaxa-Monterrey-April-28-2024-Liga-MX</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/55754ab7/Santos-Laguna-Atletico-April-28-2024-Liga-MX</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3da5acea/Necaxa-Queretaro-May-2-2024-Liga-MX</t>
